--- a/Doc/Bulk_Data_Master.xlsx
+++ b/Doc/Bulk_Data_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\Workspace\Watchcase\TTT-Jan2026\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64AA9759-A778-4321-9DA4-EF0D01DD7DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A8308F-5B26-4CC2-8CA7-8D0C9FAF8956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
